--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPI_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPI_2026_T1_Chaco.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPI_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPI_2026_T1_Chaco.xlsx
@@ -1485,7 +1485,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="BJ4" s="6" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="BJ5" s="6" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="BJ6" s="6" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="BJ7" s="6" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="BJ8" s="6" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="BJ9" s="6" t="n">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="BJ10" s="6" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="BJ11" s="6" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="BJ12" s="6" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="BJ13" s="6" t="n">
-        <v>45787</v>
+        <v>45788</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="BJ14" s="6" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="BJ15" s="6" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="BJ16" s="6" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="BJ17" s="6" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="BJ18" s="6" t="n">
-        <v>45598</v>
+        <v>45599</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="BJ19" s="6" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="BJ20" s="6" t="n">
-        <v>45779</v>
+        <v>45780</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="BJ21" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="BJ22" s="6" t="n">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45835</v>
+        <v>45836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="BJ23" s="6" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="BJ24" s="6" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="BJ25" s="6" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="BJ26" s="6" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="BJ27" s="6" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="BJ28" s="6" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="BJ29" s="6" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="BJ30" s="6" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="BJ31" s="6" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="BJ32" s="6" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         </is>
       </c>
       <c r="BJ33" s="6" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
